--- a/DesignData/Excel_Masters/KN_Balance_Master.xlsx
+++ b/DesignData/Excel_Masters/KN_Balance_Master.xlsx
@@ -8,18 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94071238B80F2F7F/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CE9A1D9-CCD0-4A0A-BF47-E50A038A243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A91A0016-6750-41AC-A34D-7095234CE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{85C5AEBD-77AB-41E4-8BED-2C34F017E60F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{85C5AEBD-77AB-41E4-8BED-2C34F017E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="DT_PlayerBaseStat" sheetId="1" r:id="rId1"/>
     <sheet name="DT_ActionCost" sheetId="2" r:id="rId2"/>
     <sheet name="DT_OverclockSetting" sheetId="3" r:id="rId3"/>
-    <sheet name="DT_PlayerComboAttack" sheetId="5" r:id="rId4"/>
-    <sheet name="DT_EnemyStats" sheetId="4" r:id="rId5"/>
-    <sheet name="DT_EnemyRanged" sheetId="6" r:id="rId6"/>
-    <sheet name="DT_BossPhase" sheetId="7" r:id="rId7"/>
+    <sheet name="DT_OverclockLv1" sheetId="8" r:id="rId4"/>
+    <sheet name="DT_PlayerComboAttack" sheetId="5" r:id="rId5"/>
+    <sheet name="DT_OverclockLv2" sheetId="9" r:id="rId6"/>
+    <sheet name="DT_OverclockLv3" sheetId="10" r:id="rId7"/>
+    <sheet name="DT_EnemyStats" sheetId="4" r:id="rId8"/>
+    <sheet name="DT_EnemyRanged" sheetId="6" r:id="rId9"/>
+    <sheet name="DT_BossPhase" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Name</t>
   </si>
@@ -86,9 +89,6 @@
     <t>Lv3Threshold</t>
   </si>
   <si>
-    <t>GainComboHit</t>
-  </si>
-  <si>
     <t>GainPerfectParry</t>
   </si>
   <si>
@@ -98,6 +98,27 @@
     <t>OverclockDecayRate</t>
   </si>
   <si>
+    <t>RowName</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>AttackSpeedAdditive</t>
+  </si>
+  <si>
+    <t>MovementSpeedAdditive</t>
+  </si>
+  <si>
+    <t>DamageMultiplier</t>
+  </si>
+  <si>
+    <t>bStaminaImmune</t>
+  </si>
+  <si>
+    <t>OverclockCost</t>
+  </si>
+  <si>
     <t>---</t>
   </si>
   <si>
@@ -113,9 +134,6 @@
     <t>ComboWindowTime</t>
   </si>
   <si>
-    <t>DamageMultiplier</t>
-  </si>
-  <si>
     <t>OverclockGain</t>
   </si>
   <si>
@@ -153,6 +171,27 @@
   </si>
   <si>
     <t>HeavyAttack_5</t>
+  </si>
+  <si>
+    <t>SlashSpeed</t>
+  </si>
+  <si>
+    <t>SlashMaxDistance</t>
+  </si>
+  <si>
+    <t>SlashDamage</t>
+  </si>
+  <si>
+    <t>GrogyDuration</t>
+  </si>
+  <si>
+    <t>TimeStopDuration</t>
+  </si>
+  <si>
+    <t>WorldTimeDilationScale</t>
+  </si>
+  <si>
+    <t>FrozenDamageMultiplier</t>
   </si>
   <si>
     <t>MoveSpeed</t>
@@ -198,7 +237,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,14 +252,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Google Sans Text"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -252,21 +283,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,26 +666,64 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>100</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>100</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>20</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>500</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>100</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C80F1B-DF9D-463D-9462-EE736A096C92}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -688,13 +754,13 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>20</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>15</v>
       </c>
     </row>
@@ -706,7 +772,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619187F8-0684-404F-A0AE-62A3A332396C}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="25.875" customWidth="1"/>
@@ -714,66 +780,59 @@
     <col min="3" max="3" width="26.125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="25.875" customWidth="1"/>
-    <col min="6" max="6" width="22.875" customWidth="1"/>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="8" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>300</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>100</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>200</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>300</v>
       </c>
-      <c r="F2" s="4">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="2">
         <v>50</v>
       </c>
-      <c r="H2" s="4">
+      <c r="G2" s="2">
         <v>40</v>
       </c>
-      <c r="I2">
+      <c r="H2">
         <v>5</v>
       </c>
     </row>
@@ -784,6 +843,70 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04C3237-30A2-4ACE-885E-F48847E9BE04}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>0.4</v>
+      </c>
+      <c r="D2">
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>1.5</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59FAAE8-FF68-4285-929C-E56FF23D3174}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -801,36 +924,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -859,7 +982,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -888,7 +1011,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -917,7 +1040,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -946,7 +1069,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -975,7 +1098,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1004,7 +1127,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -1033,7 +1156,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -1062,7 +1185,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -1091,7 +1214,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -1124,7 +1247,116 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9F9CF0-C2E6-4626-91EF-E7502CCB5AB5}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>2500</v>
+      </c>
+      <c r="C2">
+        <v>1500</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965882CF-B966-44B5-84A2-47906F58E9C8}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>1E-4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1106C0EB-B4D3-4FD5-BDF3-3D1CC07EB5F9}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -1138,42 +1370,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>40</v>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="1">
         <v>100</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>400</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>1500</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>200</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>0.5</v>
       </c>
     </row>
@@ -1183,7 +1415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50361662-C5DE-475C-9F1F-581D44BB7E03}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -1199,65 +1431,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="1">
         <v>1200</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>600</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C80F1B-DF9D-463D-9462-EE736A096C92}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/KN_Balance_Master.xlsx
+++ b/DesignData/Excel_Masters/KN_Balance_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94071238B80F2F7F/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\Katana_Neon\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A91A0016-6750-41AC-A34D-7095234CE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{85C5AEBD-77AB-41E4-8BED-2C34F017E60F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="DT_PlayerBaseStat" sheetId="1" r:id="rId1"/>
@@ -23,6 +22,8 @@
     <sheet name="DT_EnemyStats" sheetId="4" r:id="rId8"/>
     <sheet name="DT_EnemyRanged" sheetId="6" r:id="rId9"/>
     <sheet name="DT_BossPhase" sheetId="7" r:id="rId10"/>
+    <sheet name="DT_SheathComboAttack" sheetId="11" r:id="rId11"/>
+    <sheet name="DT_DrawnComboAttack" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -231,12 +232,87 @@
   </si>
   <si>
     <t>(0.7,0.4)</t>
+  </si>
+  <si>
+    <t>RequiredStance</t>
+  </si>
+  <si>
+    <t>PlayRate</t>
+  </si>
+  <si>
+    <t>MontageSectionName</t>
+  </si>
+  <si>
+    <t>Sheathed</t>
+  </si>
+  <si>
+    <t>SLight_1</t>
+  </si>
+  <si>
+    <t>SLight_2</t>
+  </si>
+  <si>
+    <t>SLight_3</t>
+  </si>
+  <si>
+    <t>SLight_4</t>
+  </si>
+  <si>
+    <t>SLight_5</t>
+  </si>
+  <si>
+    <t>SHeavy_1</t>
+  </si>
+  <si>
+    <t>SHeavy_2</t>
+  </si>
+  <si>
+    <t>SHeavy_3</t>
+  </si>
+  <si>
+    <t>SHeavy_4</t>
+  </si>
+  <si>
+    <t>SHeavy_5</t>
+  </si>
+  <si>
+    <t>Drawn</t>
+  </si>
+  <si>
+    <t>Light_1</t>
+  </si>
+  <si>
+    <t>Light_2</t>
+  </si>
+  <si>
+    <t>Light_3</t>
+  </si>
+  <si>
+    <t>Light_4</t>
+  </si>
+  <si>
+    <t>Light_5</t>
+  </si>
+  <si>
+    <t>Heavy_1</t>
+  </si>
+  <si>
+    <t>Heavy_2</t>
+  </si>
+  <si>
+    <t>Heavy_3</t>
+  </si>
+  <si>
+    <t>Heavy_4</t>
+  </si>
+  <si>
+    <t>Heavy_5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -629,7 +705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA12557-A172-43A8-814B-2A961DED2A74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -695,7 +771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C80F1B-DF9D-463D-9462-EE736A096C92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -729,11 +805,870 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>0.7</v>
+      </c>
+      <c r="H2">
+        <v>0.8</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2">
+        <v>0.18</v>
+      </c>
+      <c r="L2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>0.7</v>
+      </c>
+      <c r="H3">
+        <v>0.9</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3">
+        <v>0.18</v>
+      </c>
+      <c r="L3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>1.2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>0.6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4">
+        <v>0.2</v>
+      </c>
+      <c r="L4">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>1.2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>0.6</v>
+      </c>
+      <c r="H5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5">
+        <v>0.2</v>
+      </c>
+      <c r="L5">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6">
+        <v>0.22</v>
+      </c>
+      <c r="L6">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1.8</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L7">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>1.6</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8">
+        <v>0.26</v>
+      </c>
+      <c r="L8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9">
+        <v>0.95</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <v>1.8</v>
+      </c>
+      <c r="I9">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9">
+        <v>0.26</v>
+      </c>
+      <c r="L9">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10">
+        <v>0.95</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>0.4</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L10">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <v>0.9</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L11">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2">
+        <v>0.85</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>0.9</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2">
+        <v>0.25</v>
+      </c>
+      <c r="L2">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
+        <v>0.85</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>0.9</v>
+      </c>
+      <c r="H3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3">
+        <v>0.25</v>
+      </c>
+      <c r="L3">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>0.8</v>
+      </c>
+      <c r="H4">
+        <v>1.3</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4">
+        <v>0.27</v>
+      </c>
+      <c r="L4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>0.8</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>0.8</v>
+      </c>
+      <c r="H5">
+        <v>1.5</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5">
+        <v>0.27</v>
+      </c>
+      <c r="L5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6">
+        <v>0.75</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6">
+        <v>0.3</v>
+      </c>
+      <c r="L6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7">
+        <v>0.7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2.8</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7">
+        <v>0.35</v>
+      </c>
+      <c r="L7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8">
+        <v>0.7</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>0.7</v>
+      </c>
+      <c r="H8">
+        <v>2.4</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8">
+        <v>0.33</v>
+      </c>
+      <c r="L8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.68</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>0.7</v>
+      </c>
+      <c r="H9">
+        <v>2.6</v>
+      </c>
+      <c r="I9">
+        <v>16</v>
+      </c>
+      <c r="J9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9">
+        <v>0.33</v>
+      </c>
+      <c r="L9">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>0.65</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>0.6</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10">
+        <v>0.35</v>
+      </c>
+      <c r="L10">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11">
+        <v>0.6</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>4.5</v>
+      </c>
+      <c r="I11">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11">
+        <v>0.35</v>
+      </c>
+      <c r="L11">
+        <v>0.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DD72D5-3E18-4674-8166-A8CBBF75B080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -771,7 +1706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619187F8-0684-404F-A0AE-62A3A332396C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -843,7 +1778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04C3237-30A2-4ACE-885E-F48847E9BE04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -902,12 +1837,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59FAAE8-FF68-4285-929C-E56FF23D3174}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1248,7 +2184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9F9CF0-C2E6-4626-91EF-E7502CCB5AB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1301,12 +2237,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965882CF-B966-44B5-84A2-47906F58E9C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1352,12 +2289,13 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1106C0EB-B4D3-4FD5-BDF3-3D1CC07EB5F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1416,7 +2354,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50361662-C5DE-475C-9F1F-581D44BB7E03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
